--- a/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-06T14:52:13+00:00</t>
+    <t>2024-02-06T15:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-06T15:01:42+00:00</t>
+    <t>2024-02-06T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-06T15:02:31+00:00</t>
+    <t>2024-02-06T15:40:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-06T15:40:57+00:00</t>
+    <t>2024-02-06T16:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-06T16:15:17+00:00</t>
+    <t>2024-02-12T12:39:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/update-practitioner-qualification/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T12:39:20+00:00</t>
+    <t>2024-02-12T13:23:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
